--- a/AC_2010Bye/AC_028_vemulawada.xlsx
+++ b/AC_2010Bye/AC_028_vemulawada.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,8 +45,14 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,8 +65,26 @@
         <bgColor rgb="001F497D"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -82,11 +106,53 @@
         <color rgb="00D9D9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="001B365D"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001B365D"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -99,6 +165,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="5" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K228"/>
+  <dimension ref="A1:K230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -502,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -510,7 +592,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>PS_Serial_No</t>
+          <t>PS_Name</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -563,8 +645,10 @@
       <c r="A6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="4" t="n">
-        <v>1</v>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 1</t>
+        </is>
       </c>
       <c r="C6" s="4" t="n">
         <v>142</v>
@@ -598,8 +682,10 @@
       <c r="A7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>2</v>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 2</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>71</v>
@@ -633,8 +719,10 @@
       <c r="A8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="4" t="n">
-        <v>3</v>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 3</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>206</v>
@@ -668,8 +756,10 @@
       <c r="A9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>4</v>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 4</t>
+        </is>
       </c>
       <c r="C9" s="4" t="n">
         <v>169</v>
@@ -703,8 +793,10 @@
       <c r="A10" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="4" t="n">
-        <v>5</v>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 5</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>121</v>
@@ -738,8 +830,10 @@
       <c r="A11" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="4" t="n">
-        <v>6</v>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 6</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>78</v>
@@ -773,8 +867,10 @@
       <c r="A12" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="4" t="n">
-        <v>7</v>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 7</t>
+        </is>
       </c>
       <c r="C12" s="4" t="n">
         <v>156</v>
@@ -808,8 +904,10 @@
       <c r="A13" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="4" t="n">
-        <v>8</v>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 8</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>280</v>
@@ -843,8 +941,10 @@
       <c r="A14" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="4" t="n">
-        <v>9</v>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 9</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>332</v>
@@ -878,8 +978,10 @@
       <c r="A15" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="4" t="n">
-        <v>10</v>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 10</t>
+        </is>
       </c>
       <c r="C15" s="4" t="n">
         <v>164</v>
@@ -913,8 +1015,10 @@
       <c r="A16" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="4" t="n">
-        <v>11</v>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 11</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>66</v>
@@ -948,8 +1052,10 @@
       <c r="A17" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="4" t="n">
-        <v>12</v>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 12</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>64</v>
@@ -983,8 +1089,10 @@
       <c r="A18" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="4" t="n">
-        <v>13</v>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 13</t>
+        </is>
       </c>
       <c r="C18" s="4" t="n">
         <v>104</v>
@@ -1018,8 +1126,10 @@
       <c r="A19" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="4" t="n">
-        <v>14</v>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 14</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>113</v>
@@ -1053,8 +1163,10 @@
       <c r="A20" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="4" t="n">
-        <v>15</v>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 15</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>88</v>
@@ -1088,8 +1200,10 @@
       <c r="A21" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="4" t="n">
-        <v>16</v>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 16</t>
+        </is>
       </c>
       <c r="C21" s="4" t="n">
         <v>124</v>
@@ -1123,8 +1237,10 @@
       <c r="A22" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="4" t="n">
-        <v>17</v>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 17</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>171</v>
@@ -1158,8 +1274,10 @@
       <c r="A23" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="4" t="n">
-        <v>18</v>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 18</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>96</v>
@@ -1193,8 +1311,10 @@
       <c r="A24" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="n">
-        <v>19</v>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 19</t>
+        </is>
       </c>
       <c r="C24" s="4" t="n">
         <v>17</v>
@@ -1228,8 +1348,10 @@
       <c r="A25" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="4" t="n">
-        <v>20</v>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 20</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>92</v>
@@ -1263,8 +1385,10 @@
       <c r="A26" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="4" t="n">
-        <v>21</v>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 21</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>117</v>
@@ -1298,8 +1422,10 @@
       <c r="A27" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="4" t="n">
-        <v>22</v>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 22</t>
+        </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>69</v>
@@ -1333,8 +1459,10 @@
       <c r="A28" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="4" t="n">
-        <v>23</v>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 23</t>
+        </is>
       </c>
       <c r="C28" s="4" t="n">
         <v>172</v>
@@ -1368,8 +1496,10 @@
       <c r="A29" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="4" t="n">
-        <v>24</v>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 24</t>
+        </is>
       </c>
       <c r="C29" s="4" t="n">
         <v>184</v>
@@ -1403,8 +1533,10 @@
       <c r="A30" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B30" s="4" t="n">
-        <v>25</v>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 25</t>
+        </is>
       </c>
       <c r="C30" s="4" t="n">
         <v>88</v>
@@ -1438,8 +1570,10 @@
       <c r="A31" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B31" s="4" t="n">
-        <v>26</v>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 26</t>
+        </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>71</v>
@@ -1473,8 +1607,10 @@
       <c r="A32" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B32" s="4" t="n">
-        <v>27</v>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 27</t>
+        </is>
       </c>
       <c r="C32" s="4" t="n">
         <v>79</v>
@@ -1508,8 +1644,10 @@
       <c r="A33" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B33" s="4" t="n">
-        <v>28</v>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 28</t>
+        </is>
       </c>
       <c r="C33" s="4" t="n">
         <v>114</v>
@@ -1543,8 +1681,10 @@
       <c r="A34" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B34" s="4" t="n">
-        <v>29</v>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 29</t>
+        </is>
       </c>
       <c r="C34" s="4" t="n">
         <v>114</v>
@@ -1578,8 +1718,10 @@
       <c r="A35" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B35" s="4" t="n">
-        <v>30</v>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 30</t>
+        </is>
       </c>
       <c r="C35" s="4" t="n">
         <v>68</v>
@@ -1613,8 +1755,10 @@
       <c r="A36" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B36" s="4" t="n">
-        <v>31</v>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 31</t>
+        </is>
       </c>
       <c r="C36" s="4" t="n">
         <v>139</v>
@@ -1648,8 +1792,10 @@
       <c r="A37" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B37" s="4" t="n">
-        <v>32</v>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 32</t>
+        </is>
       </c>
       <c r="C37" s="4" t="n">
         <v>153</v>
@@ -1683,8 +1829,10 @@
       <c r="A38" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B38" s="4" t="n">
-        <v>33</v>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 33</t>
+        </is>
       </c>
       <c r="C38" s="4" t="n">
         <v>171</v>
@@ -1718,8 +1866,10 @@
       <c r="A39" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B39" s="4" t="n">
-        <v>34</v>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 34</t>
+        </is>
       </c>
       <c r="C39" s="4" t="n">
         <v>50</v>
@@ -1753,8 +1903,10 @@
       <c r="A40" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B40" s="4" t="n">
-        <v>35</v>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 35</t>
+        </is>
       </c>
       <c r="C40" s="4" t="n">
         <v>25</v>
@@ -1788,8 +1940,10 @@
       <c r="A41" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B41" s="4" t="n">
-        <v>36</v>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 36</t>
+        </is>
       </c>
       <c r="C41" s="4" t="n">
         <v>38</v>
@@ -1823,8 +1977,10 @@
       <c r="A42" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B42" s="4" t="n">
-        <v>37</v>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 37</t>
+        </is>
       </c>
       <c r="C42" s="4" t="n">
         <v>52</v>
@@ -1858,8 +2014,10 @@
       <c r="A43" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B43" s="4" t="n">
-        <v>38</v>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 38</t>
+        </is>
       </c>
       <c r="C43" s="4" t="n">
         <v>80</v>
@@ -1893,8 +2051,10 @@
       <c r="A44" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B44" s="4" t="n">
-        <v>39</v>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 39</t>
+        </is>
       </c>
       <c r="C44" s="4" t="n">
         <v>82</v>
@@ -1928,8 +2088,10 @@
       <c r="A45" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B45" s="4" t="n">
-        <v>40</v>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 40</t>
+        </is>
       </c>
       <c r="C45" s="4" t="n">
         <v>95</v>
@@ -1963,8 +2125,10 @@
       <c r="A46" s="4" t="n">
         <v>41</v>
       </c>
-      <c r="B46" s="4" t="n">
-        <v>41</v>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 41</t>
+        </is>
       </c>
       <c r="C46" s="4" t="n">
         <v>76</v>
@@ -1998,8 +2162,10 @@
       <c r="A47" s="4" t="n">
         <v>42</v>
       </c>
-      <c r="B47" s="4" t="n">
-        <v>42</v>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 42</t>
+        </is>
       </c>
       <c r="C47" s="4" t="n">
         <v>118</v>
@@ -2033,8 +2199,10 @@
       <c r="A48" s="4" t="n">
         <v>43</v>
       </c>
-      <c r="B48" s="4" t="n">
-        <v>43</v>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 43</t>
+        </is>
       </c>
       <c r="C48" s="4" t="n">
         <v>216</v>
@@ -2068,8 +2236,10 @@
       <c r="A49" s="4" t="n">
         <v>44</v>
       </c>
-      <c r="B49" s="4" t="n">
-        <v>44</v>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 44</t>
+        </is>
       </c>
       <c r="C49" s="4" t="n">
         <v>230</v>
@@ -2103,8 +2273,10 @@
       <c r="A50" s="4" t="n">
         <v>45</v>
       </c>
-      <c r="B50" s="4" t="n">
-        <v>45</v>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 45</t>
+        </is>
       </c>
       <c r="C50" s="4" t="n">
         <v>122</v>
@@ -2138,8 +2310,10 @@
       <c r="A51" s="4" t="n">
         <v>46</v>
       </c>
-      <c r="B51" s="4" t="n">
-        <v>46</v>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 46</t>
+        </is>
       </c>
       <c r="C51" s="4" t="n">
         <v>123</v>
@@ -2173,8 +2347,10 @@
       <c r="A52" s="4" t="n">
         <v>47</v>
       </c>
-      <c r="B52" s="4" t="n">
-        <v>47</v>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 47</t>
+        </is>
       </c>
       <c r="C52" s="4" t="n">
         <v>122</v>
@@ -2208,8 +2384,10 @@
       <c r="A53" s="4" t="n">
         <v>48</v>
       </c>
-      <c r="B53" s="4" t="n">
-        <v>48</v>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 48</t>
+        </is>
       </c>
       <c r="C53" s="4" t="n">
         <v>77</v>
@@ -2243,8 +2421,10 @@
       <c r="A54" s="4" t="n">
         <v>49</v>
       </c>
-      <c r="B54" s="4" t="n">
-        <v>49</v>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 49</t>
+        </is>
       </c>
       <c r="C54" s="4" t="n">
         <v>116</v>
@@ -2278,8 +2458,10 @@
       <c r="A55" s="4" t="n">
         <v>50</v>
       </c>
-      <c r="B55" s="4" t="n">
-        <v>50</v>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 50</t>
+        </is>
       </c>
       <c r="C55" s="4" t="n">
         <v>108</v>
@@ -2313,8 +2495,10 @@
       <c r="A56" s="4" t="n">
         <v>51</v>
       </c>
-      <c r="B56" s="4" t="n">
-        <v>51</v>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 51</t>
+        </is>
       </c>
       <c r="C56" s="4" t="n">
         <v>103</v>
@@ -2348,8 +2532,10 @@
       <c r="A57" s="4" t="n">
         <v>52</v>
       </c>
-      <c r="B57" s="4" t="n">
-        <v>52</v>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 52</t>
+        </is>
       </c>
       <c r="C57" s="4" t="n">
         <v>105</v>
@@ -2383,8 +2569,10 @@
       <c r="A58" s="4" t="n">
         <v>53</v>
       </c>
-      <c r="B58" s="4" t="n">
-        <v>53</v>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 53</t>
+        </is>
       </c>
       <c r="C58" s="4" t="n">
         <v>172</v>
@@ -2418,8 +2606,10 @@
       <c r="A59" s="4" t="n">
         <v>54</v>
       </c>
-      <c r="B59" s="4" t="n">
-        <v>54</v>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 54</t>
+        </is>
       </c>
       <c r="C59" s="4" t="n">
         <v>52</v>
@@ -2453,8 +2643,10 @@
       <c r="A60" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="B60" s="4" t="n">
-        <v>55</v>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 55</t>
+        </is>
       </c>
       <c r="C60" s="4" t="n">
         <v>84</v>
@@ -2488,8 +2680,10 @@
       <c r="A61" s="4" t="n">
         <v>56</v>
       </c>
-      <c r="B61" s="4" t="n">
-        <v>56</v>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 56</t>
+        </is>
       </c>
       <c r="C61" s="4" t="n">
         <v>91</v>
@@ -2523,8 +2717,10 @@
       <c r="A62" s="4" t="n">
         <v>57</v>
       </c>
-      <c r="B62" s="4" t="n">
-        <v>57</v>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 57</t>
+        </is>
       </c>
       <c r="C62" s="4" t="n">
         <v>71</v>
@@ -2558,8 +2754,10 @@
       <c r="A63" s="4" t="n">
         <v>58</v>
       </c>
-      <c r="B63" s="4" t="n">
-        <v>58</v>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 58</t>
+        </is>
       </c>
       <c r="C63" s="4" t="n">
         <v>122</v>
@@ -2593,8 +2791,10 @@
       <c r="A64" s="4" t="n">
         <v>59</v>
       </c>
-      <c r="B64" s="4" t="n">
-        <v>59</v>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 59</t>
+        </is>
       </c>
       <c r="C64" s="4" t="n">
         <v>97</v>
@@ -2628,8 +2828,10 @@
       <c r="A65" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="B65" s="4" t="n">
-        <v>60</v>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 60</t>
+        </is>
       </c>
       <c r="C65" s="4" t="n">
         <v>116</v>
@@ -2663,8 +2865,10 @@
       <c r="A66" s="4" t="n">
         <v>61</v>
       </c>
-      <c r="B66" s="4" t="n">
-        <v>61</v>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 61</t>
+        </is>
       </c>
       <c r="C66" s="4" t="n">
         <v>195</v>
@@ -2698,8 +2902,10 @@
       <c r="A67" s="4" t="n">
         <v>62</v>
       </c>
-      <c r="B67" s="4" t="n">
-        <v>62</v>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 62</t>
+        </is>
       </c>
       <c r="C67" s="4" t="n">
         <v>181</v>
@@ -2733,8 +2939,10 @@
       <c r="A68" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B68" s="4" t="n">
-        <v>63</v>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 63</t>
+        </is>
       </c>
       <c r="C68" s="4" t="n">
         <v>85</v>
@@ -2768,8 +2976,10 @@
       <c r="A69" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B69" s="4" t="n">
-        <v>64</v>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 64</t>
+        </is>
       </c>
       <c r="C69" s="4" t="n">
         <v>152</v>
@@ -2803,8 +3013,10 @@
       <c r="A70" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B70" s="4" t="n">
-        <v>65</v>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 65</t>
+        </is>
       </c>
       <c r="C70" s="4" t="n">
         <v>81</v>
@@ -2838,8 +3050,10 @@
       <c r="A71" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B71" s="4" t="n">
-        <v>66</v>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 66</t>
+        </is>
       </c>
       <c r="C71" s="4" t="n">
         <v>75</v>
@@ -2873,8 +3087,10 @@
       <c r="A72" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B72" s="4" t="n">
-        <v>67</v>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 67</t>
+        </is>
       </c>
       <c r="C72" s="4" t="n">
         <v>187</v>
@@ -2908,8 +3124,10 @@
       <c r="A73" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B73" s="4" t="n">
-        <v>68</v>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 68</t>
+        </is>
       </c>
       <c r="C73" s="4" t="n">
         <v>158</v>
@@ -2943,8 +3161,10 @@
       <c r="A74" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B74" s="4" t="n">
-        <v>69</v>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 69</t>
+        </is>
       </c>
       <c r="C74" s="4" t="n">
         <v>98</v>
@@ -2978,8 +3198,10 @@
       <c r="A75" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B75" s="4" t="n">
-        <v>70</v>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 70</t>
+        </is>
       </c>
       <c r="C75" s="4" t="n">
         <v>57</v>
@@ -3013,8 +3235,10 @@
       <c r="A76" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B76" s="4" t="n">
-        <v>71</v>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 71</t>
+        </is>
       </c>
       <c r="C76" s="4" t="n">
         <v>94</v>
@@ -3048,8 +3272,10 @@
       <c r="A77" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B77" s="4" t="n">
-        <v>72</v>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 72</t>
+        </is>
       </c>
       <c r="C77" s="4" t="n">
         <v>108</v>
@@ -3083,8 +3309,10 @@
       <c r="A78" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B78" s="4" t="n">
-        <v>73</v>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 73</t>
+        </is>
       </c>
       <c r="C78" s="4" t="n">
         <v>236</v>
@@ -3118,8 +3346,10 @@
       <c r="A79" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B79" s="4" t="n">
-        <v>74</v>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 74</t>
+        </is>
       </c>
       <c r="C79" s="4" t="n">
         <v>162</v>
@@ -3153,8 +3383,10 @@
       <c r="A80" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B80" s="4" t="n">
-        <v>75</v>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 75</t>
+        </is>
       </c>
       <c r="C80" s="4" t="n">
         <v>134</v>
@@ -3188,8 +3420,10 @@
       <c r="A81" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B81" s="4" t="n">
-        <v>76</v>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 76</t>
+        </is>
       </c>
       <c r="C81" s="4" t="n">
         <v>30</v>
@@ -3223,8 +3457,10 @@
       <c r="A82" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B82" s="4" t="n">
-        <v>77</v>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 77</t>
+        </is>
       </c>
       <c r="C82" s="4" t="n">
         <v>77</v>
@@ -3258,8 +3494,10 @@
       <c r="A83" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="B83" s="4" t="n">
-        <v>78</v>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 78</t>
+        </is>
       </c>
       <c r="C83" s="4" t="n">
         <v>63</v>
@@ -3293,8 +3531,10 @@
       <c r="A84" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="B84" s="4" t="n">
-        <v>79</v>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 79</t>
+        </is>
       </c>
       <c r="C84" s="4" t="n">
         <v>61</v>
@@ -3328,8 +3568,10 @@
       <c r="A85" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="B85" s="4" t="n">
-        <v>80</v>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 80</t>
+        </is>
       </c>
       <c r="C85" s="4" t="n">
         <v>144</v>
@@ -3363,8 +3605,10 @@
       <c r="A86" s="4" t="n">
         <v>81</v>
       </c>
-      <c r="B86" s="4" t="n">
-        <v>81</v>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 81</t>
+        </is>
       </c>
       <c r="C86" s="4" t="n">
         <v>108</v>
@@ -3398,8 +3642,10 @@
       <c r="A87" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="B87" s="4" t="n">
-        <v>82</v>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 82</t>
+        </is>
       </c>
       <c r="C87" s="4" t="n">
         <v>168</v>
@@ -3433,8 +3679,10 @@
       <c r="A88" s="4" t="n">
         <v>83</v>
       </c>
-      <c r="B88" s="4" t="n">
-        <v>83</v>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 83</t>
+        </is>
       </c>
       <c r="C88" s="4" t="n">
         <v>81</v>
@@ -3468,8 +3716,10 @@
       <c r="A89" s="4" t="n">
         <v>84</v>
       </c>
-      <c r="B89" s="4" t="n">
-        <v>84</v>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 84</t>
+        </is>
       </c>
       <c r="C89" s="4" t="n">
         <v>49</v>
@@ -3503,8 +3753,10 @@
       <c r="A90" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="B90" s="4" t="n">
-        <v>85</v>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 85</t>
+        </is>
       </c>
       <c r="C90" s="4" t="n">
         <v>65</v>
@@ -3538,8 +3790,10 @@
       <c r="A91" s="4" t="n">
         <v>86</v>
       </c>
-      <c r="B91" s="4" t="n">
-        <v>86</v>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 86</t>
+        </is>
       </c>
       <c r="C91" s="4" t="n">
         <v>32</v>
@@ -3573,8 +3827,10 @@
       <c r="A92" s="4" t="n">
         <v>87</v>
       </c>
-      <c r="B92" s="4" t="n">
-        <v>87</v>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 87</t>
+        </is>
       </c>
       <c r="C92" s="4" t="n">
         <v>198</v>
@@ -3608,8 +3864,10 @@
       <c r="A93" s="4" t="n">
         <v>88</v>
       </c>
-      <c r="B93" s="4" t="n">
-        <v>88</v>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 88</t>
+        </is>
       </c>
       <c r="C93" s="4" t="n">
         <v>315</v>
@@ -3643,8 +3901,10 @@
       <c r="A94" s="4" t="n">
         <v>89</v>
       </c>
-      <c r="B94" s="4" t="n">
-        <v>89</v>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 89</t>
+        </is>
       </c>
       <c r="C94" s="4" t="n">
         <v>279</v>
@@ -3678,8 +3938,10 @@
       <c r="A95" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="B95" s="4" t="n">
-        <v>90</v>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 90</t>
+        </is>
       </c>
       <c r="C95" s="4" t="n">
         <v>386</v>
@@ -3713,8 +3975,10 @@
       <c r="A96" s="4" t="n">
         <v>91</v>
       </c>
-      <c r="B96" s="4" t="n">
-        <v>91</v>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 91</t>
+        </is>
       </c>
       <c r="C96" s="4" t="n">
         <v>181</v>
@@ -3748,8 +4012,10 @@
       <c r="A97" s="4" t="n">
         <v>92</v>
       </c>
-      <c r="B97" s="4" t="n">
-        <v>92</v>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 92</t>
+        </is>
       </c>
       <c r="C97" s="4" t="n">
         <v>244</v>
@@ -3783,8 +4049,10 @@
       <c r="A98" s="4" t="n">
         <v>93</v>
       </c>
-      <c r="B98" s="4" t="n">
-        <v>93</v>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 93</t>
+        </is>
       </c>
       <c r="C98" s="4" t="n">
         <v>359</v>
@@ -3818,8 +4086,10 @@
       <c r="A99" s="4" t="n">
         <v>94</v>
       </c>
-      <c r="B99" s="4" t="n">
-        <v>94</v>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 94</t>
+        </is>
       </c>
       <c r="C99" s="4" t="n">
         <v>186</v>
@@ -3853,8 +4123,10 @@
       <c r="A100" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="B100" s="4" t="n">
-        <v>95</v>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 95</t>
+        </is>
       </c>
       <c r="C100" s="4" t="n">
         <v>165</v>
@@ -3888,8 +4160,10 @@
       <c r="A101" s="4" t="n">
         <v>96</v>
       </c>
-      <c r="B101" s="4" t="n">
-        <v>96</v>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 96</t>
+        </is>
       </c>
       <c r="C101" s="4" t="n">
         <v>271</v>
@@ -3923,8 +4197,10 @@
       <c r="A102" s="4" t="n">
         <v>97</v>
       </c>
-      <c r="B102" s="4" t="n">
-        <v>97</v>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 97</t>
+        </is>
       </c>
       <c r="C102" s="4" t="n">
         <v>96</v>
@@ -3958,8 +4234,10 @@
       <c r="A103" s="4" t="n">
         <v>98</v>
       </c>
-      <c r="B103" s="4" t="n">
-        <v>98</v>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 98</t>
+        </is>
       </c>
       <c r="C103" s="4" t="n">
         <v>51</v>
@@ -3993,8 +4271,10 @@
       <c r="A104" s="4" t="n">
         <v>99</v>
       </c>
-      <c r="B104" s="4" t="n">
-        <v>99</v>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 99</t>
+        </is>
       </c>
       <c r="C104" s="4" t="n">
         <v>317</v>
@@ -4028,8 +4308,10 @@
       <c r="A105" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="B105" s="4" t="n">
-        <v>100</v>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 100</t>
+        </is>
       </c>
       <c r="C105" s="4" t="n">
         <v>276</v>
@@ -4063,8 +4345,10 @@
       <c r="A106" s="4" t="n">
         <v>101</v>
       </c>
-      <c r="B106" s="4" t="n">
-        <v>101</v>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 101</t>
+        </is>
       </c>
       <c r="C106" s="4" t="n">
         <v>130</v>
@@ -4098,8 +4382,10 @@
       <c r="A107" s="4" t="n">
         <v>102</v>
       </c>
-      <c r="B107" s="4" t="n">
-        <v>102</v>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 102</t>
+        </is>
       </c>
       <c r="C107" s="4" t="n">
         <v>188</v>
@@ -4133,8 +4419,10 @@
       <c r="A108" s="4" t="n">
         <v>103</v>
       </c>
-      <c r="B108" s="4" t="n">
-        <v>103</v>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 103</t>
+        </is>
       </c>
       <c r="C108" s="4" t="n">
         <v>152</v>
@@ -4168,8 +4456,10 @@
       <c r="A109" s="4" t="n">
         <v>104</v>
       </c>
-      <c r="B109" s="4" t="n">
-        <v>104</v>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 104</t>
+        </is>
       </c>
       <c r="C109" s="4" t="n">
         <v>231</v>
@@ -4203,8 +4493,10 @@
       <c r="A110" s="4" t="n">
         <v>105</v>
       </c>
-      <c r="B110" s="4" t="n">
-        <v>105</v>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 105</t>
+        </is>
       </c>
       <c r="C110" s="4" t="n">
         <v>110</v>
@@ -4238,8 +4530,10 @@
       <c r="A111" s="4" t="n">
         <v>106</v>
       </c>
-      <c r="B111" s="4" t="n">
-        <v>106</v>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 106</t>
+        </is>
       </c>
       <c r="C111" s="4" t="n">
         <v>160</v>
@@ -4273,8 +4567,10 @@
       <c r="A112" s="4" t="n">
         <v>107</v>
       </c>
-      <c r="B112" s="4" t="n">
-        <v>107</v>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 107</t>
+        </is>
       </c>
       <c r="C112" s="4" t="n">
         <v>137</v>
@@ -4308,8 +4604,10 @@
       <c r="A113" s="4" t="n">
         <v>108</v>
       </c>
-      <c r="B113" s="4" t="n">
-        <v>108</v>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 108</t>
+        </is>
       </c>
       <c r="C113" s="4" t="n">
         <v>120</v>
@@ -4343,8 +4641,10 @@
       <c r="A114" s="4" t="n">
         <v>109</v>
       </c>
-      <c r="B114" s="4" t="n">
-        <v>109</v>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 109</t>
+        </is>
       </c>
       <c r="C114" s="4" t="n">
         <v>93</v>
@@ -4378,8 +4678,10 @@
       <c r="A115" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="B115" s="4" t="n">
-        <v>110</v>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 110</t>
+        </is>
       </c>
       <c r="C115" s="4" t="n">
         <v>162</v>
@@ -4413,8 +4715,10 @@
       <c r="A116" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="B116" s="4" t="n">
-        <v>111</v>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 111</t>
+        </is>
       </c>
       <c r="C116" s="4" t="n">
         <v>157</v>
@@ -4448,8 +4752,10 @@
       <c r="A117" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="B117" s="4" t="n">
-        <v>112</v>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 112</t>
+        </is>
       </c>
       <c r="C117" s="4" t="n">
         <v>78</v>
@@ -4483,8 +4789,10 @@
       <c r="A118" s="4" t="n">
         <v>113</v>
       </c>
-      <c r="B118" s="4" t="n">
-        <v>113</v>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 113</t>
+        </is>
       </c>
       <c r="C118" s="4" t="n">
         <v>48</v>
@@ -4518,8 +4826,10 @@
       <c r="A119" s="4" t="n">
         <v>114</v>
       </c>
-      <c r="B119" s="4" t="n">
-        <v>114</v>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 114</t>
+        </is>
       </c>
       <c r="C119" s="4" t="n">
         <v>227</v>
@@ -4553,8 +4863,10 @@
       <c r="A120" s="4" t="n">
         <v>115</v>
       </c>
-      <c r="B120" s="4" t="n">
-        <v>115</v>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 115</t>
+        </is>
       </c>
       <c r="C120" s="4" t="n">
         <v>220</v>
@@ -4588,8 +4900,10 @@
       <c r="A121" s="4" t="n">
         <v>116</v>
       </c>
-      <c r="B121" s="4" t="n">
-        <v>116</v>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 116</t>
+        </is>
       </c>
       <c r="C121" s="4" t="n">
         <v>234</v>
@@ -4623,8 +4937,10 @@
       <c r="A122" s="4" t="n">
         <v>117</v>
       </c>
-      <c r="B122" s="4" t="n">
-        <v>117</v>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 117</t>
+        </is>
       </c>
       <c r="C122" s="4" t="n">
         <v>249</v>
@@ -4658,8 +4974,10 @@
       <c r="A123" s="4" t="n">
         <v>118</v>
       </c>
-      <c r="B123" s="4" t="n">
-        <v>118</v>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 118</t>
+        </is>
       </c>
       <c r="C123" s="4" t="n">
         <v>281</v>
@@ -4693,8 +5011,10 @@
       <c r="A124" s="4" t="n">
         <v>119</v>
       </c>
-      <c r="B124" s="4" t="n">
-        <v>119</v>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 119</t>
+        </is>
       </c>
       <c r="C124" s="4" t="n">
         <v>212</v>
@@ -4728,8 +5048,10 @@
       <c r="A125" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="B125" s="4" t="n">
-        <v>120</v>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 120</t>
+        </is>
       </c>
       <c r="C125" s="4" t="n">
         <v>134</v>
@@ -4763,8 +5085,10 @@
       <c r="A126" s="4" t="n">
         <v>121</v>
       </c>
-      <c r="B126" s="4" t="n">
-        <v>121</v>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 121</t>
+        </is>
       </c>
       <c r="C126" s="4" t="n">
         <v>192</v>
@@ -4798,8 +5122,10 @@
       <c r="A127" s="4" t="n">
         <v>122</v>
       </c>
-      <c r="B127" s="4" t="n">
-        <v>122</v>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 122</t>
+        </is>
       </c>
       <c r="C127" s="4" t="n">
         <v>116</v>
@@ -4833,8 +5159,10 @@
       <c r="A128" s="4" t="n">
         <v>123</v>
       </c>
-      <c r="B128" s="4" t="n">
-        <v>123</v>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 123</t>
+        </is>
       </c>
       <c r="C128" s="4" t="n">
         <v>127</v>
@@ -4868,8 +5196,10 @@
       <c r="A129" s="4" t="n">
         <v>124</v>
       </c>
-      <c r="B129" s="4" t="n">
-        <v>124</v>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 124</t>
+        </is>
       </c>
       <c r="C129" s="4" t="n">
         <v>192</v>
@@ -4903,8 +5233,10 @@
       <c r="A130" s="4" t="n">
         <v>125</v>
       </c>
-      <c r="B130" s="4" t="n">
-        <v>125</v>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 125</t>
+        </is>
       </c>
       <c r="C130" s="4" t="n">
         <v>153</v>
@@ -4938,8 +5270,10 @@
       <c r="A131" s="4" t="n">
         <v>126</v>
       </c>
-      <c r="B131" s="4" t="n">
-        <v>126</v>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 126</t>
+        </is>
       </c>
       <c r="C131" s="4" t="n">
         <v>201</v>
@@ -4973,8 +5307,10 @@
       <c r="A132" s="4" t="n">
         <v>127</v>
       </c>
-      <c r="B132" s="4" t="n">
-        <v>127</v>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 127</t>
+        </is>
       </c>
       <c r="C132" s="4" t="n">
         <v>115</v>
@@ -5008,8 +5344,10 @@
       <c r="A133" s="4" t="n">
         <v>128</v>
       </c>
-      <c r="B133" s="4" t="n">
-        <v>128</v>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 128</t>
+        </is>
       </c>
       <c r="C133" s="4" t="n">
         <v>126</v>
@@ -5043,8 +5381,10 @@
       <c r="A134" s="4" t="n">
         <v>129</v>
       </c>
-      <c r="B134" s="4" t="n">
-        <v>129</v>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 129</t>
+        </is>
       </c>
       <c r="C134" s="4" t="n">
         <v>167</v>
@@ -5078,8 +5418,10 @@
       <c r="A135" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="B135" s="4" t="n">
-        <v>130</v>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 130</t>
+        </is>
       </c>
       <c r="C135" s="4" t="n">
         <v>170</v>
@@ -5113,8 +5455,10 @@
       <c r="A136" s="4" t="n">
         <v>131</v>
       </c>
-      <c r="B136" s="4" t="n">
-        <v>131</v>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 131</t>
+        </is>
       </c>
       <c r="C136" s="4" t="n">
         <v>191</v>
@@ -5148,8 +5492,10 @@
       <c r="A137" s="4" t="n">
         <v>132</v>
       </c>
-      <c r="B137" s="4" t="n">
-        <v>132</v>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 132</t>
+        </is>
       </c>
       <c r="C137" s="4" t="n">
         <v>120</v>
@@ -5183,8 +5529,10 @@
       <c r="A138" s="4" t="n">
         <v>133</v>
       </c>
-      <c r="B138" s="4" t="n">
-        <v>133</v>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 133</t>
+        </is>
       </c>
       <c r="C138" s="4" t="n">
         <v>49</v>
@@ -5218,8 +5566,10 @@
       <c r="A139" s="4" t="n">
         <v>134</v>
       </c>
-      <c r="B139" s="4" t="n">
-        <v>134</v>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 134</t>
+        </is>
       </c>
       <c r="C139" s="4" t="n">
         <v>174</v>
@@ -5253,8 +5603,10 @@
       <c r="A140" s="4" t="n">
         <v>135</v>
       </c>
-      <c r="B140" s="4" t="n">
-        <v>135</v>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 135</t>
+        </is>
       </c>
       <c r="C140" s="4" t="n">
         <v>234</v>
@@ -5288,8 +5640,10 @@
       <c r="A141" s="4" t="n">
         <v>136</v>
       </c>
-      <c r="B141" s="4" t="n">
-        <v>136</v>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 136</t>
+        </is>
       </c>
       <c r="C141" s="4" t="n">
         <v>146</v>
@@ -5323,8 +5677,10 @@
       <c r="A142" s="4" t="n">
         <v>137</v>
       </c>
-      <c r="B142" s="4" t="n">
-        <v>137</v>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 137</t>
+        </is>
       </c>
       <c r="C142" s="4" t="n">
         <v>127</v>
@@ -5358,8 +5714,10 @@
       <c r="A143" s="4" t="n">
         <v>138</v>
       </c>
-      <c r="B143" s="4" t="n">
-        <v>138</v>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 138</t>
+        </is>
       </c>
       <c r="C143" s="4" t="n">
         <v>144</v>
@@ -5393,8 +5751,10 @@
       <c r="A144" s="4" t="n">
         <v>139</v>
       </c>
-      <c r="B144" s="4" t="n">
-        <v>139</v>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 139</t>
+        </is>
       </c>
       <c r="C144" s="4" t="n">
         <v>58</v>
@@ -5428,8 +5788,10 @@
       <c r="A145" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="B145" s="4" t="n">
-        <v>140</v>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 140</t>
+        </is>
       </c>
       <c r="C145" s="4" t="n">
         <v>48</v>
@@ -5463,8 +5825,10 @@
       <c r="A146" s="4" t="n">
         <v>141</v>
       </c>
-      <c r="B146" s="4" t="n">
-        <v>141</v>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 141</t>
+        </is>
       </c>
       <c r="C146" s="4" t="n">
         <v>145</v>
@@ -5498,8 +5862,10 @@
       <c r="A147" s="4" t="n">
         <v>142</v>
       </c>
-      <c r="B147" s="4" t="n">
-        <v>142</v>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 142</t>
+        </is>
       </c>
       <c r="C147" s="4" t="n">
         <v>157</v>
@@ -5533,8 +5899,10 @@
       <c r="A148" s="4" t="n">
         <v>143</v>
       </c>
-      <c r="B148" s="4" t="n">
-        <v>143</v>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 143</t>
+        </is>
       </c>
       <c r="C148" s="4" t="n">
         <v>102</v>
@@ -5568,8 +5936,10 @@
       <c r="A149" s="4" t="n">
         <v>144</v>
       </c>
-      <c r="B149" s="4" t="n">
-        <v>144</v>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 144</t>
+        </is>
       </c>
       <c r="C149" s="4" t="n">
         <v>78</v>
@@ -5603,8 +5973,10 @@
       <c r="A150" s="4" t="n">
         <v>145</v>
       </c>
-      <c r="B150" s="4" t="n">
-        <v>145</v>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 145</t>
+        </is>
       </c>
       <c r="C150" s="4" t="n">
         <v>124</v>
@@ -5638,8 +6010,10 @@
       <c r="A151" s="4" t="n">
         <v>146</v>
       </c>
-      <c r="B151" s="4" t="n">
-        <v>146</v>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 146</t>
+        </is>
       </c>
       <c r="C151" s="4" t="n">
         <v>129</v>
@@ -5673,8 +6047,10 @@
       <c r="A152" s="4" t="n">
         <v>147</v>
       </c>
-      <c r="B152" s="4" t="n">
-        <v>147</v>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 147</t>
+        </is>
       </c>
       <c r="C152" s="4" t="n">
         <v>121</v>
@@ -5708,8 +6084,10 @@
       <c r="A153" s="4" t="n">
         <v>148</v>
       </c>
-      <c r="B153" s="4" t="n">
-        <v>148</v>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 148</t>
+        </is>
       </c>
       <c r="C153" s="4" t="n">
         <v>114</v>
@@ -5743,8 +6121,10 @@
       <c r="A154" s="4" t="n">
         <v>149</v>
       </c>
-      <c r="B154" s="4" t="n">
-        <v>149</v>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 149</t>
+        </is>
       </c>
       <c r="C154" s="4" t="n">
         <v>104</v>
@@ -5778,8 +6158,10 @@
       <c r="A155" s="4" t="n">
         <v>150</v>
       </c>
-      <c r="B155" s="4" t="n">
-        <v>150</v>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 150</t>
+        </is>
       </c>
       <c r="C155" s="4" t="n">
         <v>164</v>
@@ -5813,8 +6195,10 @@
       <c r="A156" s="4" t="n">
         <v>151</v>
       </c>
-      <c r="B156" s="4" t="n">
-        <v>151</v>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 151</t>
+        </is>
       </c>
       <c r="C156" s="4" t="n">
         <v>185</v>
@@ -5848,8 +6232,10 @@
       <c r="A157" s="4" t="n">
         <v>152</v>
       </c>
-      <c r="B157" s="4" t="n">
-        <v>152</v>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 152</t>
+        </is>
       </c>
       <c r="C157" s="4" t="n">
         <v>107</v>
@@ -5883,8 +6269,10 @@
       <c r="A158" s="4" t="n">
         <v>153</v>
       </c>
-      <c r="B158" s="4" t="n">
-        <v>153</v>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 153</t>
+        </is>
       </c>
       <c r="C158" s="4" t="n">
         <v>132</v>
@@ -5918,8 +6306,10 @@
       <c r="A159" s="4" t="n">
         <v>154</v>
       </c>
-      <c r="B159" s="4" t="n">
-        <v>154</v>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 154</t>
+        </is>
       </c>
       <c r="C159" s="4" t="n">
         <v>144</v>
@@ -5953,8 +6343,10 @@
       <c r="A160" s="4" t="n">
         <v>155</v>
       </c>
-      <c r="B160" s="4" t="n">
-        <v>155</v>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 155</t>
+        </is>
       </c>
       <c r="C160" s="4" t="n">
         <v>158</v>
@@ -5988,8 +6380,10 @@
       <c r="A161" s="4" t="n">
         <v>156</v>
       </c>
-      <c r="B161" s="4" t="n">
-        <v>156</v>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 156</t>
+        </is>
       </c>
       <c r="C161" s="4" t="n">
         <v>160</v>
@@ -6023,8 +6417,10 @@
       <c r="A162" s="4" t="n">
         <v>157</v>
       </c>
-      <c r="B162" s="4" t="n">
-        <v>157</v>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 157</t>
+        </is>
       </c>
       <c r="C162" s="4" t="n">
         <v>185</v>
@@ -6058,8 +6454,10 @@
       <c r="A163" s="4" t="n">
         <v>158</v>
       </c>
-      <c r="B163" s="4" t="n">
-        <v>158</v>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 158</t>
+        </is>
       </c>
       <c r="C163" s="4" t="n">
         <v>115</v>
@@ -6093,8 +6491,10 @@
       <c r="A164" s="4" t="n">
         <v>159</v>
       </c>
-      <c r="B164" s="4" t="n">
-        <v>159</v>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 159</t>
+        </is>
       </c>
       <c r="C164" s="4" t="n">
         <v>98</v>
@@ -6128,8 +6528,10 @@
       <c r="A165" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="B165" s="4" t="n">
-        <v>160</v>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 160</t>
+        </is>
       </c>
       <c r="C165" s="4" t="n">
         <v>131</v>
@@ -6163,8 +6565,10 @@
       <c r="A166" s="4" t="n">
         <v>161</v>
       </c>
-      <c r="B166" s="4" t="n">
-        <v>161</v>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 161</t>
+        </is>
       </c>
       <c r="C166" s="4" t="n">
         <v>116</v>
@@ -6198,8 +6602,10 @@
       <c r="A167" s="4" t="n">
         <v>162</v>
       </c>
-      <c r="B167" s="4" t="n">
-        <v>162</v>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 162</t>
+        </is>
       </c>
       <c r="C167" s="4" t="n">
         <v>99</v>
@@ -6233,8 +6639,10 @@
       <c r="A168" s="4" t="n">
         <v>163</v>
       </c>
-      <c r="B168" s="4" t="n">
-        <v>163</v>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 163</t>
+        </is>
       </c>
       <c r="C168" s="4" t="n">
         <v>61</v>
@@ -6268,8 +6676,10 @@
       <c r="A169" s="4" t="n">
         <v>164</v>
       </c>
-      <c r="B169" s="4" t="n">
-        <v>164</v>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 164</t>
+        </is>
       </c>
       <c r="C169" s="4" t="n">
         <v>88</v>
@@ -6303,8 +6713,10 @@
       <c r="A170" s="4" t="n">
         <v>165</v>
       </c>
-      <c r="B170" s="4" t="n">
-        <v>165</v>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 165</t>
+        </is>
       </c>
       <c r="C170" s="4" t="n">
         <v>42</v>
@@ -6338,8 +6750,10 @@
       <c r="A171" s="4" t="n">
         <v>166</v>
       </c>
-      <c r="B171" s="4" t="n">
-        <v>166</v>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 166</t>
+        </is>
       </c>
       <c r="C171" s="4" t="n">
         <v>138</v>
@@ -6373,8 +6787,10 @@
       <c r="A172" s="4" t="n">
         <v>167</v>
       </c>
-      <c r="B172" s="4" t="n">
-        <v>167</v>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 167</t>
+        </is>
       </c>
       <c r="C172" s="4" t="n">
         <v>157</v>
@@ -6408,8 +6824,10 @@
       <c r="A173" s="4" t="n">
         <v>168</v>
       </c>
-      <c r="B173" s="4" t="n">
-        <v>168</v>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 168</t>
+        </is>
       </c>
       <c r="C173" s="4" t="n">
         <v>283</v>
@@ -6443,8 +6861,10 @@
       <c r="A174" s="4" t="n">
         <v>169</v>
       </c>
-      <c r="B174" s="4" t="n">
-        <v>169</v>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 169</t>
+        </is>
       </c>
       <c r="C174" s="4" t="n">
         <v>58</v>
@@ -6478,8 +6898,10 @@
       <c r="A175" s="4" t="n">
         <v>170</v>
       </c>
-      <c r="B175" s="4" t="n">
-        <v>170</v>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 170</t>
+        </is>
       </c>
       <c r="C175" s="4" t="n">
         <v>121</v>
@@ -6513,8 +6935,10 @@
       <c r="A176" s="4" t="n">
         <v>171</v>
       </c>
-      <c r="B176" s="4" t="n">
-        <v>171</v>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 171</t>
+        </is>
       </c>
       <c r="C176" s="4" t="n">
         <v>183</v>
@@ -6548,8 +6972,10 @@
       <c r="A177" s="4" t="n">
         <v>172</v>
       </c>
-      <c r="B177" s="4" t="n">
-        <v>172</v>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 172</t>
+        </is>
       </c>
       <c r="C177" s="4" t="n">
         <v>78</v>
@@ -6583,8 +7009,10 @@
       <c r="A178" s="4" t="n">
         <v>173</v>
       </c>
-      <c r="B178" s="4" t="n">
-        <v>173</v>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 173</t>
+        </is>
       </c>
       <c r="C178" s="4" t="n">
         <v>180</v>
@@ -6618,8 +7046,10 @@
       <c r="A179" s="4" t="n">
         <v>174</v>
       </c>
-      <c r="B179" s="4" t="n">
-        <v>174</v>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 174</t>
+        </is>
       </c>
       <c r="C179" s="4" t="n">
         <v>30</v>
@@ -6653,8 +7083,10 @@
       <c r="A180" s="4" t="n">
         <v>175</v>
       </c>
-      <c r="B180" s="4" t="n">
-        <v>175</v>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 175</t>
+        </is>
       </c>
       <c r="C180" s="4" t="n">
         <v>44</v>
@@ -6688,8 +7120,10 @@
       <c r="A181" s="4" t="n">
         <v>176</v>
       </c>
-      <c r="B181" s="4" t="n">
-        <v>176</v>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 176</t>
+        </is>
       </c>
       <c r="C181" s="4" t="n">
         <v>219</v>
@@ -6723,8 +7157,10 @@
       <c r="A182" s="4" t="n">
         <v>177</v>
       </c>
-      <c r="B182" s="4" t="n">
-        <v>177</v>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 177</t>
+        </is>
       </c>
       <c r="C182" s="4" t="n">
         <v>118</v>
@@ -6758,8 +7194,10 @@
       <c r="A183" s="4" t="n">
         <v>178</v>
       </c>
-      <c r="B183" s="4" t="n">
-        <v>178</v>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 178</t>
+        </is>
       </c>
       <c r="C183" s="4" t="n">
         <v>112</v>
@@ -6793,8 +7231,10 @@
       <c r="A184" s="4" t="n">
         <v>179</v>
       </c>
-      <c r="B184" s="4" t="n">
-        <v>179</v>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 179</t>
+        </is>
       </c>
       <c r="C184" s="4" t="n">
         <v>184</v>
@@ -6828,8 +7268,10 @@
       <c r="A185" s="4" t="n">
         <v>180</v>
       </c>
-      <c r="B185" s="4" t="n">
-        <v>180</v>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 180</t>
+        </is>
       </c>
       <c r="C185" s="4" t="n">
         <v>108</v>
@@ -6863,8 +7305,10 @@
       <c r="A186" s="4" t="n">
         <v>181</v>
       </c>
-      <c r="B186" s="4" t="n">
-        <v>181</v>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 181</t>
+        </is>
       </c>
       <c r="C186" s="4" t="n">
         <v>217</v>
@@ -6898,8 +7342,10 @@
       <c r="A187" s="4" t="n">
         <v>182</v>
       </c>
-      <c r="B187" s="4" t="n">
-        <v>182</v>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 182</t>
+        </is>
       </c>
       <c r="C187" s="4" t="n">
         <v>153</v>
@@ -6933,8 +7379,10 @@
       <c r="A188" s="4" t="n">
         <v>183</v>
       </c>
-      <c r="B188" s="4" t="n">
-        <v>183</v>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 183</t>
+        </is>
       </c>
       <c r="C188" s="4" t="n">
         <v>84</v>
@@ -6968,8 +7416,10 @@
       <c r="A189" s="4" t="n">
         <v>184</v>
       </c>
-      <c r="B189" s="4" t="n">
-        <v>184</v>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 184</t>
+        </is>
       </c>
       <c r="C189" s="4" t="n">
         <v>103</v>
@@ -7003,8 +7453,10 @@
       <c r="A190" s="4" t="n">
         <v>185</v>
       </c>
-      <c r="B190" s="4" t="n">
-        <v>185</v>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 185</t>
+        </is>
       </c>
       <c r="C190" s="4" t="n">
         <v>75</v>
@@ -7038,8 +7490,10 @@
       <c r="A191" s="4" t="n">
         <v>186</v>
       </c>
-      <c r="B191" s="4" t="n">
-        <v>186</v>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 186</t>
+        </is>
       </c>
       <c r="C191" s="4" t="n">
         <v>57</v>
@@ -7073,8 +7527,10 @@
       <c r="A192" s="4" t="n">
         <v>187</v>
       </c>
-      <c r="B192" s="4" t="n">
-        <v>187</v>
+      <c r="B192" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 187</t>
+        </is>
       </c>
       <c r="C192" s="4" t="n">
         <v>81</v>
@@ -7108,8 +7564,10 @@
       <c r="A193" s="4" t="n">
         <v>188</v>
       </c>
-      <c r="B193" s="4" t="n">
-        <v>188</v>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 188</t>
+        </is>
       </c>
       <c r="C193" s="4" t="n">
         <v>176</v>
@@ -7143,8 +7601,10 @@
       <c r="A194" s="4" t="n">
         <v>189</v>
       </c>
-      <c r="B194" s="4" t="n">
-        <v>189</v>
+      <c r="B194" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 189</t>
+        </is>
       </c>
       <c r="C194" s="4" t="n">
         <v>65</v>
@@ -7178,8 +7638,10 @@
       <c r="A195" s="4" t="n">
         <v>190</v>
       </c>
-      <c r="B195" s="4" t="n">
-        <v>190</v>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 190</t>
+        </is>
       </c>
       <c r="C195" s="4" t="n">
         <v>49</v>
@@ -7213,8 +7675,10 @@
       <c r="A196" s="4" t="n">
         <v>191</v>
       </c>
-      <c r="B196" s="4" t="n">
-        <v>191</v>
+      <c r="B196" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 191</t>
+        </is>
       </c>
       <c r="C196" s="4" t="n">
         <v>54</v>
@@ -7248,8 +7712,10 @@
       <c r="A197" s="4" t="n">
         <v>192</v>
       </c>
-      <c r="B197" s="4" t="n">
-        <v>192</v>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 192</t>
+        </is>
       </c>
       <c r="C197" s="4" t="n">
         <v>80</v>
@@ -7283,8 +7749,10 @@
       <c r="A198" s="4" t="n">
         <v>193</v>
       </c>
-      <c r="B198" s="4" t="n">
-        <v>193</v>
+      <c r="B198" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 193</t>
+        </is>
       </c>
       <c r="C198" s="4" t="n">
         <v>54</v>
@@ -7318,8 +7786,10 @@
       <c r="A199" s="4" t="n">
         <v>194</v>
       </c>
-      <c r="B199" s="4" t="n">
-        <v>194</v>
+      <c r="B199" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 194</t>
+        </is>
       </c>
       <c r="C199" s="4" t="n">
         <v>185</v>
@@ -7353,8 +7823,10 @@
       <c r="A200" s="4" t="n">
         <v>195</v>
       </c>
-      <c r="B200" s="4" t="n">
-        <v>195</v>
+      <c r="B200" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 195</t>
+        </is>
       </c>
       <c r="C200" s="4" t="n">
         <v>106</v>
@@ -7388,8 +7860,10 @@
       <c r="A201" s="4" t="n">
         <v>196</v>
       </c>
-      <c r="B201" s="4" t="n">
-        <v>196</v>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 196</t>
+        </is>
       </c>
       <c r="C201" s="4" t="n">
         <v>98</v>
@@ -7423,8 +7897,10 @@
       <c r="A202" s="4" t="n">
         <v>197</v>
       </c>
-      <c r="B202" s="4" t="n">
-        <v>197</v>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 197</t>
+        </is>
       </c>
       <c r="C202" s="4" t="n">
         <v>155</v>
@@ -7458,8 +7934,10 @@
       <c r="A203" s="4" t="n">
         <v>198</v>
       </c>
-      <c r="B203" s="4" t="n">
-        <v>198</v>
+      <c r="B203" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 198</t>
+        </is>
       </c>
       <c r="C203" s="4" t="n">
         <v>175</v>
@@ -7493,8 +7971,10 @@
       <c r="A204" s="4" t="n">
         <v>199</v>
       </c>
-      <c r="B204" s="4" t="n">
-        <v>199</v>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 199</t>
+        </is>
       </c>
       <c r="C204" s="4" t="n">
         <v>104</v>
@@ -7528,8 +8008,10 @@
       <c r="A205" s="4" t="n">
         <v>200</v>
       </c>
-      <c r="B205" s="4" t="n">
-        <v>200</v>
+      <c r="B205" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 200</t>
+        </is>
       </c>
       <c r="C205" s="4" t="n">
         <v>94</v>
@@ -7563,8 +8045,10 @@
       <c r="A206" s="4" t="n">
         <v>201</v>
       </c>
-      <c r="B206" s="4" t="n">
-        <v>201</v>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 201</t>
+        </is>
       </c>
       <c r="C206" s="4" t="n">
         <v>49</v>
@@ -7598,8 +8082,10 @@
       <c r="A207" s="4" t="n">
         <v>202</v>
       </c>
-      <c r="B207" s="4" t="n">
-        <v>202</v>
+      <c r="B207" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 202</t>
+        </is>
       </c>
       <c r="C207" s="4" t="n">
         <v>137</v>
@@ -7633,8 +8119,10 @@
       <c r="A208" s="4" t="n">
         <v>203</v>
       </c>
-      <c r="B208" s="4" t="n">
-        <v>203</v>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 203</t>
+        </is>
       </c>
       <c r="C208" s="4" t="n">
         <v>50</v>
@@ -7668,8 +8156,10 @@
       <c r="A209" s="4" t="n">
         <v>204</v>
       </c>
-      <c r="B209" s="4" t="n">
-        <v>204</v>
+      <c r="B209" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 204</t>
+        </is>
       </c>
       <c r="C209" s="4" t="n">
         <v>46</v>
@@ -7703,8 +8193,10 @@
       <c r="A210" s="4" t="n">
         <v>205</v>
       </c>
-      <c r="B210" s="4" t="n">
-        <v>205</v>
+      <c r="B210" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 205</t>
+        </is>
       </c>
       <c r="C210" s="4" t="n">
         <v>103</v>
@@ -7738,8 +8230,10 @@
       <c r="A211" s="4" t="n">
         <v>206</v>
       </c>
-      <c r="B211" s="4" t="n">
-        <v>206</v>
+      <c r="B211" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 206</t>
+        </is>
       </c>
       <c r="C211" s="4" t="n">
         <v>73</v>
@@ -7773,8 +8267,10 @@
       <c r="A212" s="4" t="n">
         <v>207</v>
       </c>
-      <c r="B212" s="4" t="n">
-        <v>207</v>
+      <c r="B212" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 207</t>
+        </is>
       </c>
       <c r="C212" s="4" t="n">
         <v>113</v>
@@ -7808,8 +8304,10 @@
       <c r="A213" s="4" t="n">
         <v>208</v>
       </c>
-      <c r="B213" s="4" t="n">
-        <v>208</v>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 208</t>
+        </is>
       </c>
       <c r="C213" s="4" t="n">
         <v>68</v>
@@ -7843,8 +8341,10 @@
       <c r="A214" s="4" t="n">
         <v>209</v>
       </c>
-      <c r="B214" s="4" t="n">
-        <v>209</v>
+      <c r="B214" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 209</t>
+        </is>
       </c>
       <c r="C214" s="4" t="n">
         <v>58</v>
@@ -7878,8 +8378,10 @@
       <c r="A215" s="4" t="n">
         <v>210</v>
       </c>
-      <c r="B215" s="4" t="n">
-        <v>210</v>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 210</t>
+        </is>
       </c>
       <c r="C215" s="4" t="n">
         <v>98</v>
@@ -7913,8 +8415,10 @@
       <c r="A216" s="4" t="n">
         <v>211</v>
       </c>
-      <c r="B216" s="4" t="n">
-        <v>211</v>
+      <c r="B216" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 211</t>
+        </is>
       </c>
       <c r="C216" s="4" t="n">
         <v>77</v>
@@ -7948,8 +8452,10 @@
       <c r="A217" s="4" t="n">
         <v>212</v>
       </c>
-      <c r="B217" s="4" t="n">
-        <v>212</v>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 212</t>
+        </is>
       </c>
       <c r="C217" s="4" t="n">
         <v>118</v>
@@ -7983,8 +8489,10 @@
       <c r="A218" s="4" t="n">
         <v>213</v>
       </c>
-      <c r="B218" s="4" t="n">
-        <v>213</v>
+      <c r="B218" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 213</t>
+        </is>
       </c>
       <c r="C218" s="4" t="n">
         <v>133</v>
@@ -8018,8 +8526,10 @@
       <c r="A219" s="4" t="n">
         <v>214</v>
       </c>
-      <c r="B219" s="4" t="n">
-        <v>214</v>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 214</t>
+        </is>
       </c>
       <c r="C219" s="4" t="n">
         <v>134</v>
@@ -8053,8 +8563,10 @@
       <c r="A220" s="4" t="n">
         <v>215</v>
       </c>
-      <c r="B220" s="4" t="n">
-        <v>215</v>
+      <c r="B220" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 215</t>
+        </is>
       </c>
       <c r="C220" s="4" t="n">
         <v>51</v>
@@ -8088,8 +8600,10 @@
       <c r="A221" s="4" t="n">
         <v>216</v>
       </c>
-      <c r="B221" s="4" t="n">
-        <v>216</v>
+      <c r="B221" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 216</t>
+        </is>
       </c>
       <c r="C221" s="4" t="n">
         <v>95</v>
@@ -8123,8 +8637,10 @@
       <c r="A222" s="4" t="n">
         <v>217</v>
       </c>
-      <c r="B222" s="4" t="n">
-        <v>217</v>
+      <c r="B222" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 217</t>
+        </is>
       </c>
       <c r="C222" s="4" t="n">
         <v>131</v>
@@ -8158,8 +8674,10 @@
       <c r="A223" s="4" t="n">
         <v>218</v>
       </c>
-      <c r="B223" s="4" t="n">
-        <v>218</v>
+      <c r="B223" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 218</t>
+        </is>
       </c>
       <c r="C223" s="4" t="n">
         <v>77</v>
@@ -8193,8 +8711,10 @@
       <c r="A224" s="4" t="n">
         <v>219</v>
       </c>
-      <c r="B224" s="4" t="n">
-        <v>219</v>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 219</t>
+        </is>
       </c>
       <c r="C224" s="4" t="n">
         <v>47</v>
@@ -8228,8 +8748,10 @@
       <c r="A225" s="4" t="n">
         <v>220</v>
       </c>
-      <c r="B225" s="4" t="n">
-        <v>220</v>
+      <c r="B225" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 220</t>
+        </is>
       </c>
       <c r="C225" s="4" t="n">
         <v>175</v>
@@ -8263,8 +8785,10 @@
       <c r="A226" s="4" t="n">
         <v>221</v>
       </c>
-      <c r="B226" s="4" t="n">
-        <v>221</v>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 221</t>
+        </is>
       </c>
       <c r="C226" s="4" t="n">
         <v>173</v>
@@ -8298,8 +8822,10 @@
       <c r="A227" s="4" t="n">
         <v>222</v>
       </c>
-      <c r="B227" s="4" t="n">
-        <v>222</v>
+      <c r="B227" s="4" t="inlineStr">
+        <is>
+          <t>Vemulawada PS 222</t>
+        </is>
       </c>
       <c r="C227" s="4" t="n">
         <v>128</v>
@@ -8330,45 +8856,125 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B228" s="6">
-        <f>SUM(B6:B227)</f>
-        <v/>
-      </c>
-      <c r="C228" s="6">
+      <c r="A228" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL EVM VOTES</t>
+        </is>
+      </c>
+      <c r="B228" s="12" t="inlineStr"/>
+      <c r="C228" s="13">
         <f>SUM(C6:C227)</f>
         <v/>
       </c>
-      <c r="D228" s="6">
+      <c r="D228" s="13">
         <f>SUM(D6:D227)</f>
         <v/>
       </c>
-      <c r="E228" s="6">
+      <c r="E228" s="13">
         <f>SUM(E6:E227)</f>
         <v/>
       </c>
-      <c r="F228" s="6">
+      <c r="F228" s="13">
         <f>SUM(F6:F227)</f>
         <v/>
       </c>
-      <c r="G228" s="6">
+      <c r="G228" s="13">
         <f>SUM(G6:G227)</f>
         <v/>
       </c>
-      <c r="H228" s="6">
+      <c r="H228" s="13">
         <f>SUM(H6:H227)</f>
         <v/>
       </c>
-      <c r="I228" s="6">
+      <c r="I228" s="13">
         <f>SUM(I6:I227)</f>
         <v/>
       </c>
-      <c r="J228" s="6">
+      <c r="J228" s="13">
         <f>SUM(J6:J227)</f>
+        <v/>
+      </c>
+      <c r="K228" s="13">
+        <f>SUM(K6:K227)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="8" t="inlineStr">
+        <is>
+          <t>POSTAL BALLOT VOTES</t>
+        </is>
+      </c>
+      <c r="B229" s="9" t="inlineStr"/>
+      <c r="C229" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D229" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="F229" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="9" t="n">
+        <v>110</v>
+      </c>
+      <c r="H229" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I229" s="9" t="n">
+        <v>111</v>
+      </c>
+      <c r="J229" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="10" t="inlineStr">
+        <is>
+          <t>TOTAL VOTES POLLED</t>
+        </is>
+      </c>
+      <c r="B230" s="11" t="inlineStr"/>
+      <c r="C230" s="11">
+        <f>C228+C229</f>
+        <v/>
+      </c>
+      <c r="D230" s="11">
+        <f>D228+D229</f>
+        <v/>
+      </c>
+      <c r="E230" s="11">
+        <f>E228+E229</f>
+        <v/>
+      </c>
+      <c r="F230" s="11">
+        <f>F228+F229</f>
+        <v/>
+      </c>
+      <c r="G230" s="11">
+        <f>G228+G229</f>
+        <v/>
+      </c>
+      <c r="H230" s="11">
+        <f>H228+H229</f>
+        <v/>
+      </c>
+      <c r="I230" s="11">
+        <f>I228+I229</f>
+        <v/>
+      </c>
+      <c r="J230" s="11">
+        <f>J228+J229</f>
+        <v/>
+      </c>
+      <c r="K230" s="11">
+        <f>K228+K229</f>
         <v/>
       </c>
     </row>

--- a/AC_2010Bye/AC_028_vemulawada.xlsx
+++ b/AC_2010Bye/AC_028_vemulawada.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="6">
@@ -84,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -148,11 +153,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -179,6 +192,27 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -583,7 +617,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
@@ -8856,124 +8889,124 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="7" t="inlineStr">
+      <c r="A228" s="14" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B228" s="12" t="inlineStr"/>
-      <c r="C228" s="13">
+      <c r="B228" s="15" t="inlineStr"/>
+      <c r="C228" s="16">
         <f>SUM(C6:C227)</f>
         <v/>
       </c>
-      <c r="D228" s="13">
+      <c r="D228" s="16">
         <f>SUM(D6:D227)</f>
         <v/>
       </c>
-      <c r="E228" s="13">
+      <c r="E228" s="16">
         <f>SUM(E6:E227)</f>
         <v/>
       </c>
-      <c r="F228" s="13">
+      <c r="F228" s="16">
         <f>SUM(F6:F227)</f>
         <v/>
       </c>
-      <c r="G228" s="13">
+      <c r="G228" s="16">
         <f>SUM(G6:G227)</f>
         <v/>
       </c>
-      <c r="H228" s="13">
+      <c r="H228" s="16">
         <f>SUM(H6:H227)</f>
         <v/>
       </c>
-      <c r="I228" s="13">
+      <c r="I228" s="16">
         <f>SUM(I6:I227)</f>
         <v/>
       </c>
-      <c r="J228" s="13">
+      <c r="J228" s="16">
         <f>SUM(J6:J227)</f>
         <v/>
       </c>
-      <c r="K228" s="13">
+      <c r="K228" s="16">
         <f>SUM(K6:K227)</f>
         <v/>
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="8" t="inlineStr">
+      <c r="A229" s="17" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B229" s="9" t="inlineStr"/>
-      <c r="C229" s="9" t="n">
+      <c r="C229" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="D229" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E229" s="9" t="n">
+      <c r="D229" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" s="16" t="n">
         <v>100</v>
       </c>
-      <c r="F229" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G229" s="9" t="n">
+      <c r="F229" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G229" s="16" t="n">
         <v>110</v>
       </c>
-      <c r="H229" s="9" t="n">
+      <c r="H229" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="I229" s="9" t="n">
+      <c r="I229" s="16" t="n">
         <v>111</v>
       </c>
-      <c r="J229" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K229" s="9" t="n">
+      <c r="J229" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K229" s="16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="10" t="inlineStr">
+      <c r="A230" s="18" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B230" s="11" t="inlineStr"/>
-      <c r="C230" s="11">
+      <c r="B230" s="19" t="inlineStr"/>
+      <c r="C230" s="20">
         <f>C228+C229</f>
         <v/>
       </c>
-      <c r="D230" s="11">
+      <c r="D230" s="20">
         <f>D228+D229</f>
         <v/>
       </c>
-      <c r="E230" s="11">
+      <c r="E230" s="20">
         <f>E228+E229</f>
         <v/>
       </c>
-      <c r="F230" s="11">
+      <c r="F230" s="20">
         <f>F228+F229</f>
         <v/>
       </c>
-      <c r="G230" s="11">
+      <c r="G230" s="20">
         <f>G228+G229</f>
         <v/>
       </c>
-      <c r="H230" s="11">
+      <c r="H230" s="20">
         <f>H228+H229</f>
         <v/>
       </c>
-      <c r="I230" s="11">
+      <c r="I230" s="20">
         <f>I228+I229</f>
         <v/>
       </c>
-      <c r="J230" s="11">
+      <c r="J230" s="20">
         <f>J228+J229</f>
         <v/>
       </c>
-      <c r="K230" s="11">
+      <c r="K230" s="20">
         <f>K228+K229</f>
         <v/>
       </c>
